--- a/data/Finger_Pressure_Acupuncture_and_Moxacauterization/data.xlsx
+++ b/data/Finger_Pressure_Acupuncture_and_Moxacauterization/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\itfile01\保健医療政策課\オープンデータ\あはき（0114）\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ivpf201v.takamatsu.local\Profile\52845\Documents\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C972F88-9CB0-40C0-A781-FB77055D91C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B91682B-821E-45CE-A2A2-17EAEBFF81BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3010,19 +3010,19 @@
     <t>168</t>
   </si>
   <si>
-    <t>ハーリー治療院</t>
-  </si>
-  <si>
     <t>立川　雅之</t>
   </si>
   <si>
-    <t>34.315920</t>
-  </si>
-  <si>
-    <t>134.071406</t>
-  </si>
-  <si>
-    <t>2012/08/02</t>
+    <t>34.319980</t>
+  </si>
+  <si>
+    <t>134.076086</t>
+  </si>
+  <si>
+    <t>高松市木太町１５１７－２</t>
+  </si>
+  <si>
+    <t>2026/04/03</t>
   </si>
   <si>
     <t>169</t>
@@ -5287,7 +5287,7 @@
     <t>134.078285</t>
   </si>
   <si>
-    <t>高松市木太町３４４３－１７</t>
+    <t>高松市木太町３４４３−１７</t>
   </si>
   <si>
     <t>2026/07/20</t>
@@ -6313,6 +6313,13 @@
     <t>2026/05/06</t>
   </si>
   <si>
+    <t>ハーリー施術院</t>
+    <rPh sb="4" eb="6">
+      <t>セジュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>高松市花ノ宮町二丁目12-18</t>
   </si>
   <si>
@@ -6800,9 +6807,6 @@
   </si>
   <si>
     <t>高松市香南町横井７６０番地６</t>
-  </si>
-  <si>
-    <t>高松市木太町８７７番地３</t>
   </si>
   <si>
     <t>高松市木太町１９０３番地１２</t>
@@ -7353,7 +7357,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -7694,12 +7698,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L352"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="55.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7737,7 +7741,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -7754,7 +7758,7 @@
         <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="G2" t="s">
         <v>17</v>
@@ -7775,7 +7779,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -7792,7 +7796,7 @@
         <v>24</v>
       </c>
       <c r="F3" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="G3" t="s">
         <v>25</v>
@@ -7813,7 +7817,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -7830,7 +7834,7 @@
         <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="G4" t="s">
         <v>31</v>
@@ -7851,7 +7855,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -7868,7 +7872,7 @@
         <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="G5" t="s">
         <v>37</v>
@@ -7889,7 +7893,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -7906,7 +7910,7 @@
         <v>42</v>
       </c>
       <c r="F6" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="G6" t="s">
         <v>43</v>
@@ -7927,7 +7931,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>44</v>
       </c>
@@ -7944,7 +7948,7 @@
         <v>48</v>
       </c>
       <c r="F7" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="G7" t="s">
         <v>49</v>
@@ -7965,7 +7969,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>50</v>
       </c>
@@ -7982,7 +7986,7 @@
         <v>54</v>
       </c>
       <c r="F8" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="G8" t="s">
         <v>55</v>
@@ -8003,7 +8007,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>56</v>
       </c>
@@ -8020,7 +8024,7 @@
         <v>60</v>
       </c>
       <c r="F9" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="G9" t="s">
         <v>61</v>
@@ -8041,7 +8045,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>62</v>
       </c>
@@ -8058,7 +8062,7 @@
         <v>66</v>
       </c>
       <c r="F10" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="G10" t="s">
         <v>67</v>
@@ -8079,7 +8083,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>68</v>
       </c>
@@ -8096,7 +8100,7 @@
         <v>72</v>
       </c>
       <c r="F11" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="G11" t="s">
         <v>73</v>
@@ -8117,7 +8121,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>74</v>
       </c>
@@ -8134,7 +8138,7 @@
         <v>78</v>
       </c>
       <c r="F12" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="G12" t="s">
         <v>79</v>
@@ -8155,7 +8159,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>80</v>
       </c>
@@ -8172,7 +8176,7 @@
         <v>84</v>
       </c>
       <c r="F13" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="G13" t="s">
         <v>85</v>
@@ -8193,7 +8197,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>86</v>
       </c>
@@ -8210,7 +8214,7 @@
         <v>90</v>
       </c>
       <c r="F14" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="G14" t="s">
         <v>91</v>
@@ -8231,7 +8235,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>92</v>
       </c>
@@ -8248,7 +8252,7 @@
         <v>96</v>
       </c>
       <c r="F15" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="G15" t="s">
         <v>97</v>
@@ -8269,7 +8273,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>98</v>
       </c>
@@ -8286,7 +8290,7 @@
         <v>101</v>
       </c>
       <c r="F16" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="G16" t="s">
         <v>97</v>
@@ -8307,7 +8311,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>102</v>
       </c>
@@ -8324,7 +8328,7 @@
         <v>105</v>
       </c>
       <c r="F17" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="G17" t="s">
         <v>97</v>
@@ -8345,7 +8349,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>106</v>
       </c>
@@ -8362,7 +8366,7 @@
         <v>109</v>
       </c>
       <c r="F18" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="G18" t="s">
         <v>97</v>
@@ -8383,7 +8387,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>110</v>
       </c>
@@ -8400,7 +8404,7 @@
         <v>114</v>
       </c>
       <c r="F19" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="G19" t="s">
         <v>115</v>
@@ -8421,7 +8425,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>116</v>
       </c>
@@ -8438,7 +8442,7 @@
         <v>120</v>
       </c>
       <c r="F20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="G20" t="s">
         <v>121</v>
@@ -8459,7 +8463,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>122</v>
       </c>
@@ -8476,7 +8480,7 @@
         <v>126</v>
       </c>
       <c r="F21" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="G21" t="s">
         <v>127</v>
@@ -8497,7 +8501,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>128</v>
       </c>
@@ -8514,7 +8518,7 @@
         <v>132</v>
       </c>
       <c r="F22" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="G22" t="s">
         <v>133</v>
@@ -8535,7 +8539,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>134</v>
       </c>
@@ -8552,7 +8556,7 @@
         <v>138</v>
       </c>
       <c r="F23" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="G23" t="s">
         <v>139</v>
@@ -8573,7 +8577,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>140</v>
       </c>
@@ -8590,7 +8594,7 @@
         <v>144</v>
       </c>
       <c r="F24" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="G24" t="s">
         <v>145</v>
@@ -8611,7 +8615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>146</v>
       </c>
@@ -8628,7 +8632,7 @@
         <v>150</v>
       </c>
       <c r="F25" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="G25" t="s">
         <v>151</v>
@@ -8649,7 +8653,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>152</v>
       </c>
@@ -8666,7 +8670,7 @@
         <v>156</v>
       </c>
       <c r="F26" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="G26" t="s">
         <v>157</v>
@@ -8687,7 +8691,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>158</v>
       </c>
@@ -8704,7 +8708,7 @@
         <v>162</v>
       </c>
       <c r="F27" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="G27" t="s">
         <v>163</v>
@@ -8725,7 +8729,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>164</v>
       </c>
@@ -8742,7 +8746,7 @@
         <v>168</v>
       </c>
       <c r="F28" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="G28" t="s">
         <v>169</v>
@@ -8763,7 +8767,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>170</v>
       </c>
@@ -8780,7 +8784,7 @@
         <v>174</v>
       </c>
       <c r="F29" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="G29" t="s">
         <v>175</v>
@@ -8801,7 +8805,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>176</v>
       </c>
@@ -8818,7 +8822,7 @@
         <v>180</v>
       </c>
       <c r="F30" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="G30" t="s">
         <v>181</v>
@@ -8839,7 +8843,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>182</v>
       </c>
@@ -8856,7 +8860,7 @@
         <v>186</v>
       </c>
       <c r="F31" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="G31" t="s">
         <v>187</v>
@@ -8877,7 +8881,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>188</v>
       </c>
@@ -8894,7 +8898,7 @@
         <v>192</v>
       </c>
       <c r="F32" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="G32" t="s">
         <v>193</v>
@@ -8915,7 +8919,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>194</v>
       </c>
@@ -8932,7 +8936,7 @@
         <v>198</v>
       </c>
       <c r="F33" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="G33" t="s">
         <v>199</v>
@@ -8953,7 +8957,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>200</v>
       </c>
@@ -8970,7 +8974,7 @@
         <v>204</v>
       </c>
       <c r="F34" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="G34" t="s">
         <v>205</v>
@@ -8991,7 +8995,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>206</v>
       </c>
@@ -9029,7 +9033,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>213</v>
       </c>
@@ -9046,7 +9050,7 @@
         <v>217</v>
       </c>
       <c r="F36" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="G36" t="s">
         <v>218</v>
@@ -9067,7 +9071,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>219</v>
       </c>
@@ -9084,7 +9088,7 @@
         <v>223</v>
       </c>
       <c r="F37" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="G37" t="s">
         <v>224</v>
@@ -9105,7 +9109,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>225</v>
       </c>
@@ -9122,7 +9126,7 @@
         <v>228</v>
       </c>
       <c r="F38" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="G38" t="s">
         <v>229</v>
@@ -9143,7 +9147,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>231</v>
       </c>
@@ -9160,7 +9164,7 @@
         <v>235</v>
       </c>
       <c r="F39" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="G39" t="s">
         <v>236</v>
@@ -9181,7 +9185,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>237</v>
       </c>
@@ -9198,7 +9202,7 @@
         <v>241</v>
       </c>
       <c r="F40" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="G40" t="s">
         <v>242</v>
@@ -9219,7 +9223,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>243</v>
       </c>
@@ -9236,7 +9240,7 @@
         <v>247</v>
       </c>
       <c r="F41" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="G41" t="s">
         <v>248</v>
@@ -9257,7 +9261,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>249</v>
       </c>
@@ -9274,7 +9278,7 @@
         <v>253</v>
       </c>
       <c r="F42" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="G42" t="s">
         <v>254</v>
@@ -9295,7 +9299,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>255</v>
       </c>
@@ -9312,7 +9316,7 @@
         <v>259</v>
       </c>
       <c r="F43" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="G43" t="s">
         <v>260</v>
@@ -9333,7 +9337,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>261</v>
       </c>
@@ -9350,7 +9354,7 @@
         <v>265</v>
       </c>
       <c r="F44" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G44" t="s">
         <v>266</v>
@@ -9371,7 +9375,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>267</v>
       </c>
@@ -9388,7 +9392,7 @@
         <v>271</v>
       </c>
       <c r="F45" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="G45" t="s">
         <v>272</v>
@@ -9409,7 +9413,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>273</v>
       </c>
@@ -9426,7 +9430,7 @@
         <v>277</v>
       </c>
       <c r="F46" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="G46" t="s">
         <v>278</v>
@@ -9447,7 +9451,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>279</v>
       </c>
@@ -9464,7 +9468,7 @@
         <v>283</v>
       </c>
       <c r="F47" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="G47" t="s">
         <v>284</v>
@@ -9485,7 +9489,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>285</v>
       </c>
@@ -9502,7 +9506,7 @@
         <v>289</v>
       </c>
       <c r="F48" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="G48" t="s">
         <v>290</v>
@@ -9523,7 +9527,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>291</v>
       </c>
@@ -9540,7 +9544,7 @@
         <v>295</v>
       </c>
       <c r="F49" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="G49" t="s">
         <v>296</v>
@@ -9561,7 +9565,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>297</v>
       </c>
@@ -9599,7 +9603,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>304</v>
       </c>
@@ -9616,7 +9620,7 @@
         <v>308</v>
       </c>
       <c r="F51" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="G51" t="s">
         <v>309</v>
@@ -9637,7 +9641,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>310</v>
       </c>
@@ -9654,7 +9658,7 @@
         <v>314</v>
       </c>
       <c r="F52" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="G52" t="s">
         <v>315</v>
@@ -9675,7 +9679,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>316</v>
       </c>
@@ -9692,7 +9696,7 @@
         <v>320</v>
       </c>
       <c r="F53" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="G53" t="s">
         <v>321</v>
@@ -9713,7 +9717,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>322</v>
       </c>
@@ -9730,7 +9734,7 @@
         <v>326</v>
       </c>
       <c r="F54" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="G54" t="s">
         <v>327</v>
@@ -9751,7 +9755,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>328</v>
       </c>
@@ -9768,7 +9772,7 @@
         <v>332</v>
       </c>
       <c r="F55" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="G55" t="s">
         <v>333</v>
@@ -9789,7 +9793,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>334</v>
       </c>
@@ -9806,7 +9810,7 @@
         <v>338</v>
       </c>
       <c r="F56" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="G56" t="s">
         <v>339</v>
@@ -9827,7 +9831,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>340</v>
       </c>
@@ -9844,7 +9848,7 @@
         <v>344</v>
       </c>
       <c r="F57" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="G57" t="s">
         <v>345</v>
@@ -9865,7 +9869,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>346</v>
       </c>
@@ -9882,7 +9886,7 @@
         <v>350</v>
       </c>
       <c r="F58" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="G58" t="s">
         <v>351</v>
@@ -9903,7 +9907,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>352</v>
       </c>
@@ -9920,7 +9924,7 @@
         <v>356</v>
       </c>
       <c r="F59" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="G59" t="s">
         <v>357</v>
@@ -9941,7 +9945,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>358</v>
       </c>
@@ -9958,7 +9962,7 @@
         <v>362</v>
       </c>
       <c r="F60" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="G60" t="s">
         <v>363</v>
@@ -9979,7 +9983,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>364</v>
       </c>
@@ -9996,7 +10000,7 @@
         <v>368</v>
       </c>
       <c r="F61" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="G61" t="s">
         <v>369</v>
@@ -10017,7 +10021,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>370</v>
       </c>
@@ -10034,7 +10038,7 @@
         <v>374</v>
       </c>
       <c r="F62" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="G62" t="s">
         <v>375</v>
@@ -10055,7 +10059,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>376</v>
       </c>
@@ -10072,7 +10076,7 @@
         <v>380</v>
       </c>
       <c r="F63" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="G63" t="s">
         <v>381</v>
@@ -10093,7 +10097,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>382</v>
       </c>
@@ -10110,7 +10114,7 @@
         <v>386</v>
       </c>
       <c r="F64" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="G64" t="s">
         <v>387</v>
@@ -10131,7 +10135,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>388</v>
       </c>
@@ -10148,7 +10152,7 @@
         <v>391</v>
       </c>
       <c r="F65" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="G65" t="s">
         <v>392</v>
@@ -10169,7 +10173,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>393</v>
       </c>
@@ -10186,7 +10190,7 @@
         <v>397</v>
       </c>
       <c r="F66" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="G66" t="s">
         <v>398</v>
@@ -10207,7 +10211,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>399</v>
       </c>
@@ -10224,7 +10228,7 @@
         <v>403</v>
       </c>
       <c r="F67" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="G67" t="s">
         <v>404</v>
@@ -10245,7 +10249,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>405</v>
       </c>
@@ -10262,7 +10266,7 @@
         <v>409</v>
       </c>
       <c r="F68" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="G68" t="s">
         <v>410</v>
@@ -10283,7 +10287,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>411</v>
       </c>
@@ -10300,7 +10304,7 @@
         <v>415</v>
       </c>
       <c r="F69" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="G69" t="s">
         <v>416</v>
@@ -10321,7 +10325,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>417</v>
       </c>
@@ -10338,7 +10342,7 @@
         <v>421</v>
       </c>
       <c r="F70" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="G70" t="s">
         <v>422</v>
@@ -10359,7 +10363,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>423</v>
       </c>
@@ -10376,7 +10380,7 @@
         <v>426</v>
       </c>
       <c r="F71" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="G71" t="s">
         <v>427</v>
@@ -10397,7 +10401,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>428</v>
       </c>
@@ -10414,7 +10418,7 @@
         <v>432</v>
       </c>
       <c r="F72" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="G72" t="s">
         <v>433</v>
@@ -10435,7 +10439,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>434</v>
       </c>
@@ -10452,7 +10456,7 @@
         <v>437</v>
       </c>
       <c r="F73" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="G73" t="s">
         <v>438</v>
@@ -10473,7 +10477,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>439</v>
       </c>
@@ -10490,7 +10494,7 @@
         <v>443</v>
       </c>
       <c r="F74" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="G74" t="s">
         <v>444</v>
@@ -10511,7 +10515,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>445</v>
       </c>
@@ -10528,7 +10532,7 @@
         <v>449</v>
       </c>
       <c r="F75" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="G75" t="s">
         <v>450</v>
@@ -10549,7 +10553,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>451</v>
       </c>
@@ -10566,7 +10570,7 @@
         <v>455</v>
       </c>
       <c r="F76" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="G76" t="s">
         <v>456</v>
@@ -10587,7 +10591,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>457</v>
       </c>
@@ -10604,7 +10608,7 @@
         <v>461</v>
       </c>
       <c r="F77" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="G77" t="s">
         <v>462</v>
@@ -10625,7 +10629,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>463</v>
       </c>
@@ -10642,7 +10646,7 @@
         <v>467</v>
       </c>
       <c r="F78" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="G78" t="s">
         <v>468</v>
@@ -10663,7 +10667,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>469</v>
       </c>
@@ -10680,7 +10684,7 @@
         <v>473</v>
       </c>
       <c r="F79" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="G79" t="s">
         <v>474</v>
@@ -10701,7 +10705,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>475</v>
       </c>
@@ -10718,7 +10722,7 @@
         <v>479</v>
       </c>
       <c r="F80" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="G80" t="s">
         <v>480</v>
@@ -10739,7 +10743,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>481</v>
       </c>
@@ -10756,7 +10760,7 @@
         <v>485</v>
       </c>
       <c r="F81" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="G81" t="s">
         <v>486</v>
@@ -10777,7 +10781,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>487</v>
       </c>
@@ -10794,7 +10798,7 @@
         <v>491</v>
       </c>
       <c r="F82" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="G82" t="s">
         <v>492</v>
@@ -10815,7 +10819,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>493</v>
       </c>
@@ -10832,7 +10836,7 @@
         <v>497</v>
       </c>
       <c r="F83" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="G83" t="s">
         <v>498</v>
@@ -10853,7 +10857,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>499</v>
       </c>
@@ -10870,7 +10874,7 @@
         <v>503</v>
       </c>
       <c r="F84" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="G84" t="s">
         <v>504</v>
@@ -10891,7 +10895,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>505</v>
       </c>
@@ -10908,7 +10912,7 @@
         <v>509</v>
       </c>
       <c r="F85" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="G85" t="s">
         <v>510</v>
@@ -10929,7 +10933,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>511</v>
       </c>
@@ -10946,7 +10950,7 @@
         <v>515</v>
       </c>
       <c r="F86" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="G86" t="s">
         <v>516</v>
@@ -10967,7 +10971,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>517</v>
       </c>
@@ -10984,7 +10988,7 @@
         <v>521</v>
       </c>
       <c r="F87" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="G87" t="s">
         <v>522</v>
@@ -11005,7 +11009,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>523</v>
       </c>
@@ -11022,7 +11026,7 @@
         <v>527</v>
       </c>
       <c r="F88" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="G88" t="s">
         <v>528</v>
@@ -11043,7 +11047,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>529</v>
       </c>
@@ -11060,7 +11064,7 @@
         <v>533</v>
       </c>
       <c r="F89" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="G89" t="s">
         <v>534</v>
@@ -11081,7 +11085,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>535</v>
       </c>
@@ -11098,7 +11102,7 @@
         <v>539</v>
       </c>
       <c r="F90" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="G90" t="s">
         <v>540</v>
@@ -11119,7 +11123,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>541</v>
       </c>
@@ -11136,7 +11140,7 @@
         <v>545</v>
       </c>
       <c r="F91" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="G91" t="s">
         <v>546</v>
@@ -11157,7 +11161,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>547</v>
       </c>
@@ -11174,7 +11178,7 @@
         <v>551</v>
       </c>
       <c r="F92" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="G92" t="s">
         <v>552</v>
@@ -11195,7 +11199,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>553</v>
       </c>
@@ -11212,7 +11216,7 @@
         <v>557</v>
       </c>
       <c r="F93" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="G93" t="s">
         <v>558</v>
@@ -11233,7 +11237,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>559</v>
       </c>
@@ -11250,7 +11254,7 @@
         <v>563</v>
       </c>
       <c r="F94" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="G94" t="s">
         <v>564</v>
@@ -11271,7 +11275,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>565</v>
       </c>
@@ -11288,7 +11292,7 @@
         <v>569</v>
       </c>
       <c r="F95" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="G95" t="s">
         <v>570</v>
@@ -11309,7 +11313,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>571</v>
       </c>
@@ -11326,7 +11330,7 @@
         <v>575</v>
       </c>
       <c r="F96" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="G96" t="s">
         <v>576</v>
@@ -11347,7 +11351,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>577</v>
       </c>
@@ -11364,7 +11368,7 @@
         <v>581</v>
       </c>
       <c r="F97" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="G97" t="s">
         <v>582</v>
@@ -11385,7 +11389,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>583</v>
       </c>
@@ -11402,7 +11406,7 @@
         <v>587</v>
       </c>
       <c r="F98" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="G98" t="s">
         <v>588</v>
@@ -11423,7 +11427,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>589</v>
       </c>
@@ -11440,7 +11444,7 @@
         <v>593</v>
       </c>
       <c r="F99" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="G99" t="s">
         <v>594</v>
@@ -11461,7 +11465,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>595</v>
       </c>
@@ -11478,7 +11482,7 @@
         <v>599</v>
       </c>
       <c r="F100" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="G100" t="s">
         <v>600</v>
@@ -11499,7 +11503,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>601</v>
       </c>
@@ -11516,7 +11520,7 @@
         <v>605</v>
       </c>
       <c r="F101" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="G101" t="s">
         <v>606</v>
@@ -11537,7 +11541,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>607</v>
       </c>
@@ -11554,7 +11558,7 @@
         <v>611</v>
       </c>
       <c r="F102" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="G102" t="s">
         <v>612</v>
@@ -11575,7 +11579,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>613</v>
       </c>
@@ -11592,7 +11596,7 @@
         <v>616</v>
       </c>
       <c r="F103" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="G103" t="s">
         <v>410</v>
@@ -11613,7 +11617,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>617</v>
       </c>
@@ -11630,7 +11634,7 @@
         <v>621</v>
       </c>
       <c r="F104" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="G104" t="s">
         <v>622</v>
@@ -11651,7 +11655,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>623</v>
       </c>
@@ -11668,7 +11672,7 @@
         <v>627</v>
       </c>
       <c r="F105" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="G105" t="s">
         <v>628</v>
@@ -11689,7 +11693,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>629</v>
       </c>
@@ -11706,7 +11710,7 @@
         <v>633</v>
       </c>
       <c r="F106" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="G106" t="s">
         <v>634</v>
@@ -11727,7 +11731,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>635</v>
       </c>
@@ -11744,7 +11748,7 @@
         <v>639</v>
       </c>
       <c r="F107" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="G107" t="s">
         <v>640</v>
@@ -11765,7 +11769,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>641</v>
       </c>
@@ -11782,7 +11786,7 @@
         <v>645</v>
       </c>
       <c r="F108" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="G108" t="s">
         <v>646</v>
@@ -11803,7 +11807,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>647</v>
       </c>
@@ -11820,7 +11824,7 @@
         <v>651</v>
       </c>
       <c r="F109" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="G109" t="s">
         <v>652</v>
@@ -11841,7 +11845,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>653</v>
       </c>
@@ -11858,7 +11862,7 @@
         <v>657</v>
       </c>
       <c r="F110" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="G110" t="s">
         <v>658</v>
@@ -11879,7 +11883,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>659</v>
       </c>
@@ -11896,7 +11900,7 @@
         <v>663</v>
       </c>
       <c r="F111" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="G111" t="s">
         <v>664</v>
@@ -11917,7 +11921,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>665</v>
       </c>
@@ -11934,7 +11938,7 @@
         <v>669</v>
       </c>
       <c r="F112" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="G112" t="s">
         <v>670</v>
@@ -11955,7 +11959,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>671</v>
       </c>
@@ -11972,7 +11976,7 @@
         <v>674</v>
       </c>
       <c r="F113" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="G113" t="s">
         <v>675</v>
@@ -11993,7 +11997,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>676</v>
       </c>
@@ -12010,7 +12014,7 @@
         <v>680</v>
       </c>
       <c r="F114" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="G114" t="s">
         <v>681</v>
@@ -12031,7 +12035,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>682</v>
       </c>
@@ -12048,7 +12052,7 @@
         <v>686</v>
       </c>
       <c r="F115" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="G115" t="s">
         <v>687</v>
@@ -12069,7 +12073,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>688</v>
       </c>
@@ -12086,7 +12090,7 @@
         <v>692</v>
       </c>
       <c r="F116" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="G116" t="s">
         <v>693</v>
@@ -12107,7 +12111,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>694</v>
       </c>
@@ -12124,7 +12128,7 @@
         <v>698</v>
       </c>
       <c r="F117" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="G117" t="s">
         <v>699</v>
@@ -12145,7 +12149,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>700</v>
       </c>
@@ -12162,7 +12166,7 @@
         <v>704</v>
       </c>
       <c r="F118" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="G118" t="s">
         <v>705</v>
@@ -12183,7 +12187,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>706</v>
       </c>
@@ -12200,7 +12204,7 @@
         <v>710</v>
       </c>
       <c r="F119" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="G119" t="s">
         <v>711</v>
@@ -12221,7 +12225,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>712</v>
       </c>
@@ -12238,7 +12242,7 @@
         <v>716</v>
       </c>
       <c r="F120" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="G120" t="s">
         <v>717</v>
@@ -12259,7 +12263,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>718</v>
       </c>
@@ -12276,7 +12280,7 @@
         <v>722</v>
       </c>
       <c r="F121" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="G121" t="s">
         <v>723</v>
@@ -12297,7 +12301,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>724</v>
       </c>
@@ -12314,7 +12318,7 @@
         <v>728</v>
       </c>
       <c r="F122" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="G122" t="s">
         <v>729</v>
@@ -12335,7 +12339,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>730</v>
       </c>
@@ -12352,7 +12356,7 @@
         <v>734</v>
       </c>
       <c r="F123" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="G123" t="s">
         <v>735</v>
@@ -12373,7 +12377,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>736</v>
       </c>
@@ -12390,7 +12394,7 @@
         <v>740</v>
       </c>
       <c r="F124" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="G124" t="s">
         <v>741</v>
@@ -12411,7 +12415,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>742</v>
       </c>
@@ -12428,7 +12432,7 @@
         <v>746</v>
       </c>
       <c r="F125" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="G125" t="s">
         <v>747</v>
@@ -12449,7 +12453,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>748</v>
       </c>
@@ -12466,7 +12470,7 @@
         <v>752</v>
       </c>
       <c r="F126" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="G126" t="s">
         <v>753</v>
@@ -12487,7 +12491,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>754</v>
       </c>
@@ -12504,7 +12508,7 @@
         <v>758</v>
       </c>
       <c r="F127" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="G127" t="s">
         <v>759</v>
@@ -12525,7 +12529,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>760</v>
       </c>
@@ -12542,7 +12546,7 @@
         <v>764</v>
       </c>
       <c r="F128" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="G128" t="s">
         <v>765</v>
@@ -12563,7 +12567,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>766</v>
       </c>
@@ -12580,7 +12584,7 @@
         <v>770</v>
       </c>
       <c r="F129" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="G129" t="s">
         <v>55</v>
@@ -12601,7 +12605,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>771</v>
       </c>
@@ -12618,7 +12622,7 @@
         <v>775</v>
       </c>
       <c r="F130" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="G130" t="s">
         <v>776</v>
@@ -12639,7 +12643,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>777</v>
       </c>
@@ -12677,7 +12681,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>784</v>
       </c>
@@ -12694,7 +12698,7 @@
         <v>788</v>
       </c>
       <c r="F132" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="G132" t="s">
         <v>789</v>
@@ -12715,7 +12719,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>790</v>
       </c>
@@ -12732,7 +12736,7 @@
         <v>794</v>
       </c>
       <c r="F133" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="G133" t="s">
         <v>795</v>
@@ -12753,7 +12757,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>796</v>
       </c>
@@ -12770,7 +12774,7 @@
         <v>800</v>
       </c>
       <c r="F134" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="G134" t="s">
         <v>801</v>
@@ -12791,7 +12795,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>802</v>
       </c>
@@ -12808,7 +12812,7 @@
         <v>806</v>
       </c>
       <c r="F135" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="G135" t="s">
         <v>807</v>
@@ -12829,7 +12833,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>808</v>
       </c>
@@ -12846,7 +12850,7 @@
         <v>812</v>
       </c>
       <c r="F136" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="G136" t="s">
         <v>813</v>
@@ -12867,7 +12871,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>814</v>
       </c>
@@ -12884,7 +12888,7 @@
         <v>818</v>
       </c>
       <c r="F137" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="G137" t="s">
         <v>819</v>
@@ -12905,7 +12909,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>820</v>
       </c>
@@ -12922,7 +12926,7 @@
         <v>824</v>
       </c>
       <c r="F138" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="G138" t="s">
         <v>825</v>
@@ -12943,7 +12947,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>826</v>
       </c>
@@ -12960,7 +12964,7 @@
         <v>830</v>
       </c>
       <c r="F139" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="G139" t="s">
         <v>831</v>
@@ -12981,7 +12985,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>832</v>
       </c>
@@ -12998,7 +13002,7 @@
         <v>836</v>
       </c>
       <c r="F140" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="G140" t="s">
         <v>837</v>
@@ -13019,7 +13023,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>838</v>
       </c>
@@ -13036,7 +13040,7 @@
         <v>842</v>
       </c>
       <c r="F141" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="G141" t="s">
         <v>843</v>
@@ -13057,7 +13061,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>844</v>
       </c>
@@ -13074,7 +13078,7 @@
         <v>848</v>
       </c>
       <c r="F142" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
       <c r="G142" t="s">
         <v>849</v>
@@ -13095,7 +13099,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>850</v>
       </c>
@@ -13112,7 +13116,7 @@
         <v>853</v>
       </c>
       <c r="F143" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="G143" t="s">
         <v>854</v>
@@ -13133,7 +13137,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>855</v>
       </c>
@@ -13150,7 +13154,7 @@
         <v>859</v>
       </c>
       <c r="F144" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
       <c r="G144" t="s">
         <v>860</v>
@@ -13171,7 +13175,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>861</v>
       </c>
@@ -13188,7 +13192,7 @@
         <v>865</v>
       </c>
       <c r="F145" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="G145" t="s">
         <v>866</v>
@@ -13209,7 +13213,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>867</v>
       </c>
@@ -13226,7 +13230,7 @@
         <v>871</v>
       </c>
       <c r="F146" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="G146" t="s">
         <v>872</v>
@@ -13247,7 +13251,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>873</v>
       </c>
@@ -13264,7 +13268,7 @@
         <v>877</v>
       </c>
       <c r="F147" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="G147" t="s">
         <v>878</v>
@@ -13285,7 +13289,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>879</v>
       </c>
@@ -13302,7 +13306,7 @@
         <v>883</v>
       </c>
       <c r="F148" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="G148" t="s">
         <v>884</v>
@@ -13323,7 +13327,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>885</v>
       </c>
@@ -13340,7 +13344,7 @@
         <v>889</v>
       </c>
       <c r="F149" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="G149" t="s">
         <v>890</v>
@@ -13361,7 +13365,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>891</v>
       </c>
@@ -13378,7 +13382,7 @@
         <v>895</v>
       </c>
       <c r="F150" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="G150" t="s">
         <v>896</v>
@@ -13399,7 +13403,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>897</v>
       </c>
@@ -13416,7 +13420,7 @@
         <v>901</v>
       </c>
       <c r="F151" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="G151" t="s">
         <v>866</v>
@@ -13437,7 +13441,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>902</v>
       </c>
@@ -13454,7 +13458,7 @@
         <v>905</v>
       </c>
       <c r="F152" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="G152" t="s">
         <v>866</v>
@@ -13475,7 +13479,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>906</v>
       </c>
@@ -13492,7 +13496,7 @@
         <v>910</v>
       </c>
       <c r="F153" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="G153" t="s">
         <v>911</v>
@@ -13513,7 +13517,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>912</v>
       </c>
@@ -13530,7 +13534,7 @@
         <v>916</v>
       </c>
       <c r="F154" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="G154" t="s">
         <v>917</v>
@@ -13551,7 +13555,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>918</v>
       </c>
@@ -13568,7 +13572,7 @@
         <v>922</v>
       </c>
       <c r="F155" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="G155" t="s">
         <v>923</v>
@@ -13589,7 +13593,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>924</v>
       </c>
@@ -13606,7 +13610,7 @@
         <v>928</v>
       </c>
       <c r="F156" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="G156" t="s">
         <v>929</v>
@@ -13627,7 +13631,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>930</v>
       </c>
@@ -13644,7 +13648,7 @@
         <v>934</v>
       </c>
       <c r="F157" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="G157" t="s">
         <v>935</v>
@@ -13665,7 +13669,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>936</v>
       </c>
@@ -13682,7 +13686,7 @@
         <v>940</v>
       </c>
       <c r="F158" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="G158" t="s">
         <v>19</v>
@@ -13703,7 +13707,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>941</v>
       </c>
@@ -13720,7 +13724,7 @@
         <v>945</v>
       </c>
       <c r="F159" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="G159" t="s">
         <v>946</v>
@@ -13741,7 +13745,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>947</v>
       </c>
@@ -13758,7 +13762,7 @@
         <v>951</v>
       </c>
       <c r="F160" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="G160" t="s">
         <v>952</v>
@@ -13779,7 +13783,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>953</v>
       </c>
@@ -13796,7 +13800,7 @@
         <v>957</v>
       </c>
       <c r="F161" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="G161" t="s">
         <v>958</v>
@@ -13817,7 +13821,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>959</v>
       </c>
@@ -13834,7 +13838,7 @@
         <v>963</v>
       </c>
       <c r="F162" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="G162" t="s">
         <v>964</v>
@@ -13855,7 +13859,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>966</v>
       </c>
@@ -13872,7 +13876,7 @@
         <v>970</v>
       </c>
       <c r="F163" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="G163" t="s">
         <v>971</v>
@@ -13893,7 +13897,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>972</v>
       </c>
@@ -13910,7 +13914,7 @@
         <v>976</v>
       </c>
       <c r="F164" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
       <c r="G164" t="s">
         <v>977</v>
@@ -13931,7 +13935,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>978</v>
       </c>
@@ -13948,7 +13952,7 @@
         <v>982</v>
       </c>
       <c r="F165" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="G165" t="s">
         <v>983</v>
@@ -13969,7 +13973,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>984</v>
       </c>
@@ -13986,7 +13990,7 @@
         <v>988</v>
       </c>
       <c r="F166" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="G166" t="s">
         <v>989</v>
@@ -14007,7 +14011,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>990</v>
       </c>
@@ -14024,7 +14028,7 @@
         <v>994</v>
       </c>
       <c r="F167" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="G167" t="s">
         <v>872</v>
@@ -14045,24 +14049,24 @@
         <v>19</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>995</v>
       </c>
       <c r="B168" t="s">
+        <v>2097</v>
+      </c>
+      <c r="C168" t="s">
         <v>996</v>
       </c>
-      <c r="C168" t="s">
+      <c r="D168" t="s">
         <v>997</v>
       </c>
-      <c r="D168" t="s">
+      <c r="E168" t="s">
         <v>998</v>
       </c>
-      <c r="E168" t="s">
+      <c r="F168" t="s">
         <v>999</v>
-      </c>
-      <c r="F168" t="s">
-        <v>2260</v>
       </c>
       <c r="G168" t="s">
         <v>1000</v>
@@ -14083,7 +14087,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>1001</v>
       </c>
@@ -14121,7 +14125,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>1007</v>
       </c>
@@ -14159,7 +14163,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="171" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>1013</v>
       </c>
@@ -14197,7 +14201,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="172" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>1019</v>
       </c>
@@ -14235,7 +14239,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="173" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>1024</v>
       </c>
@@ -14273,7 +14277,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="174" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>1029</v>
       </c>
@@ -14311,7 +14315,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="175" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>1035</v>
       </c>
@@ -14349,7 +14353,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="176" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>1041</v>
       </c>
@@ -14387,7 +14391,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="177" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>1047</v>
       </c>
@@ -14425,7 +14429,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="178" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>1053</v>
       </c>
@@ -14463,7 +14467,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="179" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>1059</v>
       </c>
@@ -14501,7 +14505,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>1065</v>
       </c>
@@ -14539,7 +14543,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="181" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>1071</v>
       </c>
@@ -14577,7 +14581,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="182" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>1077</v>
       </c>
@@ -14615,7 +14619,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="183" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>1083</v>
       </c>
@@ -14653,7 +14657,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="184" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>1089</v>
       </c>
@@ -14691,7 +14695,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="185" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>1095</v>
       </c>
@@ -14729,7 +14733,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>1101</v>
       </c>
@@ -14767,7 +14771,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="187" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>1107</v>
       </c>
@@ -14805,7 +14809,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="188" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>1113</v>
       </c>
@@ -14843,7 +14847,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>1119</v>
       </c>
@@ -14881,7 +14885,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>1125</v>
       </c>
@@ -14919,7 +14923,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>1131</v>
       </c>
@@ -14957,7 +14961,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="192" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>1136</v>
       </c>
@@ -14995,7 +14999,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="193" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>1142</v>
       </c>
@@ -15033,7 +15037,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="194" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>1148</v>
       </c>
@@ -15071,7 +15075,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="195" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>1154</v>
       </c>
@@ -15109,7 +15113,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="196" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>1160</v>
       </c>
@@ -15147,7 +15151,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="197" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>1166</v>
       </c>
@@ -15185,7 +15189,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="198" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>1172</v>
       </c>
@@ -15223,7 +15227,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="199" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>1178</v>
       </c>
@@ -15261,7 +15265,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="200" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>1184</v>
       </c>
@@ -15299,7 +15303,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="201" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>1190</v>
       </c>
@@ -15337,7 +15341,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="202" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>1196</v>
       </c>
@@ -15375,7 +15379,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>1202</v>
       </c>
@@ -15413,7 +15417,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>1208</v>
       </c>
@@ -15451,7 +15455,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="205" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>1214</v>
       </c>
@@ -15489,7 +15493,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="206" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>1219</v>
       </c>
@@ -15527,7 +15531,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="207" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>1224</v>
       </c>
@@ -15565,7 +15569,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="208" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>1230</v>
       </c>
@@ -15603,7 +15607,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="209" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>1236</v>
       </c>
@@ -15641,7 +15645,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="210" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>1242</v>
       </c>
@@ -15679,7 +15683,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="211" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>1248</v>
       </c>
@@ -15717,7 +15721,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="212" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>1254</v>
       </c>
@@ -15755,7 +15759,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="213" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>1260</v>
       </c>
@@ -15793,7 +15797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="214" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>1265</v>
       </c>
@@ -15831,7 +15835,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="215" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>1271</v>
       </c>
@@ -15869,7 +15873,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="216" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>1277</v>
       </c>
@@ -15907,7 +15911,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="217" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>1283</v>
       </c>
@@ -15945,7 +15949,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="218" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>1289</v>
       </c>
@@ -15983,7 +15987,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="219" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>1295</v>
       </c>
@@ -16021,7 +16025,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="220" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>1301</v>
       </c>
@@ -16059,7 +16063,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="221" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>1307</v>
       </c>
@@ -16097,7 +16101,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="222" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>1313</v>
       </c>
@@ -16135,7 +16139,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="223" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>1319</v>
       </c>
@@ -16173,7 +16177,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="224" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>1324</v>
       </c>
@@ -16211,7 +16215,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="225" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>1330</v>
       </c>
@@ -16249,7 +16253,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="226" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>1336</v>
       </c>
@@ -16287,7 +16291,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="227" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>1342</v>
       </c>
@@ -16325,7 +16329,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="228" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>1348</v>
       </c>
@@ -16363,7 +16367,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="229" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>1354</v>
       </c>
@@ -16401,7 +16405,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="230" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>1360</v>
       </c>
@@ -16439,7 +16443,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="231" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>1367</v>
       </c>
@@ -16477,7 +16481,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="232" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>1373</v>
       </c>
@@ -16515,7 +16519,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="233" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>1379</v>
       </c>
@@ -16553,7 +16557,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="234" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>1385</v>
       </c>
@@ -16591,7 +16595,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="235" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>1391</v>
       </c>
@@ -16629,7 +16633,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="236" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>1397</v>
       </c>
@@ -16667,7 +16671,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="237" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>1403</v>
       </c>
@@ -16705,7 +16709,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="238" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>1409</v>
       </c>
@@ -16743,7 +16747,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="239" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>1415</v>
       </c>
@@ -16781,7 +16785,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="240" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>1421</v>
       </c>
@@ -16819,7 +16823,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="241" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>1427</v>
       </c>
@@ -16857,7 +16861,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="242" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>1432</v>
       </c>
@@ -16895,7 +16899,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="243" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>1438</v>
       </c>
@@ -16933,7 +16937,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="244" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>1444</v>
       </c>
@@ -16971,7 +16975,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="245" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>1449</v>
       </c>
@@ -17009,7 +17013,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="246" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>1455</v>
       </c>
@@ -17047,7 +17051,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="247" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>1461</v>
       </c>
@@ -17085,7 +17089,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="248" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>1467</v>
       </c>
@@ -17123,7 +17127,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="249" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>1473</v>
       </c>
@@ -17161,7 +17165,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="250" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>1478</v>
       </c>
@@ -17199,7 +17203,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="251" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>1484</v>
       </c>
@@ -17237,7 +17241,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="252" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>1490</v>
       </c>
@@ -17275,7 +17279,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="253" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>1495</v>
       </c>
@@ -17313,7 +17317,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="254" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>1501</v>
       </c>
@@ -17351,7 +17355,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="255" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>1507</v>
       </c>
@@ -17389,7 +17393,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="256" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>1513</v>
       </c>
@@ -17427,7 +17431,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="257" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>1519</v>
       </c>
@@ -17465,7 +17469,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="258" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>1525</v>
       </c>
@@ -17503,7 +17507,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="259" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>1531</v>
       </c>
@@ -17541,7 +17545,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="260" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>1537</v>
       </c>
@@ -17579,7 +17583,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="261" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>1543</v>
       </c>
@@ -17617,7 +17621,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="262" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>1549</v>
       </c>
@@ -17655,7 +17659,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="263" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>1555</v>
       </c>
@@ -17693,7 +17697,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="264" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>1561</v>
       </c>
@@ -17731,7 +17735,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="265" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>1567</v>
       </c>
@@ -17769,7 +17773,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="266" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>1573</v>
       </c>
@@ -17807,7 +17811,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="267" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>1579</v>
       </c>
@@ -17845,7 +17849,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="268" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>1584</v>
       </c>
@@ -17883,7 +17887,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="269" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>1590</v>
       </c>
@@ -17921,7 +17925,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="270" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>1596</v>
       </c>
@@ -17959,7 +17963,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="271" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>1602</v>
       </c>
@@ -17997,7 +18001,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="272" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>1608</v>
       </c>
@@ -18035,7 +18039,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="273" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>1615</v>
       </c>
@@ -18073,7 +18077,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="274" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>1621</v>
       </c>
@@ -18111,7 +18115,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="275" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>1626</v>
       </c>
@@ -18149,7 +18153,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="276" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>1632</v>
       </c>
@@ -18187,7 +18191,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="277" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>1638</v>
       </c>
@@ -18225,7 +18229,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="278" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>1644</v>
       </c>
@@ -18263,7 +18267,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="279" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>1650</v>
       </c>
@@ -18301,7 +18305,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="280" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>1656</v>
       </c>
@@ -18339,7 +18343,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="281" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>1662</v>
       </c>
@@ -18377,7 +18381,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="282" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>1668</v>
       </c>
@@ -18415,7 +18419,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="283" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>1674</v>
       </c>
@@ -18453,7 +18457,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="284" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>1680</v>
       </c>
@@ -18491,7 +18495,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="285" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>1686</v>
       </c>
@@ -18529,7 +18533,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="286" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>1691</v>
       </c>
@@ -18567,7 +18571,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="287" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>1697</v>
       </c>
@@ -18605,7 +18609,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="288" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>1703</v>
       </c>
@@ -18643,7 +18647,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="289" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>1709</v>
       </c>
@@ -18681,7 +18685,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="290" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>1715</v>
       </c>
@@ -18719,7 +18723,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="291" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>1720</v>
       </c>
@@ -18757,7 +18761,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="292" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>1726</v>
       </c>
@@ -18795,7 +18799,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="293" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>1732</v>
       </c>
@@ -18833,7 +18837,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="294" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>1738</v>
       </c>
@@ -18871,7 +18875,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="295" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>1744</v>
       </c>
@@ -18909,7 +18913,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="296" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>1750</v>
       </c>
@@ -18947,7 +18951,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="297" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>1757</v>
       </c>
@@ -18985,7 +18989,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="298" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>1763</v>
       </c>
@@ -19023,7 +19027,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="299" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>1769</v>
       </c>
@@ -19061,7 +19065,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="300" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>1774</v>
       </c>
@@ -19099,7 +19103,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="301" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>1779</v>
       </c>
@@ -19137,7 +19141,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="302" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>1785</v>
       </c>
@@ -19175,7 +19179,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="303" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>1791</v>
       </c>
@@ -19213,7 +19217,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="304" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>1797</v>
       </c>
@@ -19251,7 +19255,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="305" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>1803</v>
       </c>
@@ -19289,7 +19293,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="306" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>1808</v>
       </c>
@@ -19327,7 +19331,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="307" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>1814</v>
       </c>
@@ -19365,7 +19369,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="308" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>1820</v>
       </c>
@@ -19403,7 +19407,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="309" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>1826</v>
       </c>
@@ -19441,7 +19445,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="310" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>1832</v>
       </c>
@@ -19479,7 +19483,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="311" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>1838</v>
       </c>
@@ -19517,7 +19521,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="312" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>1844</v>
       </c>
@@ -19555,7 +19559,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="313" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>1850</v>
       </c>
@@ -19593,7 +19597,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="314" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>1856</v>
       </c>
@@ -19631,7 +19635,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="315" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>1862</v>
       </c>
@@ -19669,7 +19673,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="316" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>1868</v>
       </c>
@@ -19707,7 +19711,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="317" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>1874</v>
       </c>
@@ -19745,7 +19749,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="318" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>1880</v>
       </c>
@@ -19783,7 +19787,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="319" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>1885</v>
       </c>
@@ -19821,7 +19825,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="320" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>1891</v>
       </c>
@@ -19859,7 +19863,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="321" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>1897</v>
       </c>
@@ -19897,7 +19901,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="322" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>1902</v>
       </c>
@@ -19935,7 +19939,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="323" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>1908</v>
       </c>
@@ -19973,7 +19977,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="324" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>1914</v>
       </c>
@@ -20011,7 +20015,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="325" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>1920</v>
       </c>
@@ -20049,7 +20053,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="326" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>1926</v>
       </c>
@@ -20087,7 +20091,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="327" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>1932</v>
       </c>
@@ -20125,7 +20129,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="328" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>1938</v>
       </c>
@@ -20163,7 +20167,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="329" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>1944</v>
       </c>
@@ -20201,7 +20205,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="330" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>1949</v>
       </c>
@@ -20239,7 +20243,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="331" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>1955</v>
       </c>
@@ -20277,7 +20281,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="332" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>1961</v>
       </c>
@@ -20315,7 +20319,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="333" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>1967</v>
       </c>
@@ -20353,7 +20357,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="334" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>1973</v>
       </c>
@@ -20391,7 +20395,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="335" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>1979</v>
       </c>
@@ -20429,7 +20433,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="336" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>1985</v>
       </c>
@@ -20467,7 +20471,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="337" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>1991</v>
       </c>
@@ -20505,7 +20509,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="338" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>1997</v>
       </c>
@@ -20543,7 +20547,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="339" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>2003</v>
       </c>
@@ -20581,7 +20585,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="340" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>2009</v>
       </c>
@@ -20619,7 +20623,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="341" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>2015</v>
       </c>
@@ -20657,7 +20661,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="342" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>2022</v>
       </c>
@@ -20695,7 +20699,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="343" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>2029</v>
       </c>
@@ -20733,7 +20737,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="344" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>2036</v>
       </c>
@@ -20771,7 +20775,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="345" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>2043</v>
       </c>
@@ -20809,7 +20813,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="346" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>2050</v>
       </c>
@@ -20847,7 +20851,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="347" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>2057</v>
       </c>
@@ -20885,7 +20889,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="348" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>2064</v>
       </c>
@@ -20923,7 +20927,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="349" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>2071</v>
       </c>
@@ -20961,7 +20965,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="350" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>2078</v>
       </c>
@@ -20999,7 +21003,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="351" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>2084</v>
       </c>
@@ -21037,7 +21041,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="352" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>2090</v>
       </c>
@@ -21079,7 +21083,7 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:L1 A35:L35 A2:E2 G2:L2 A3:E3 G3:L3 A4:E4 G4:L4 A5:E5 G5:L5 A6:E6 G6:L6 A7:E7 G7:L7 A8:E8 G8:L8 A9:E9 G9:L9 A10:E10 G10:L10 A11:E11 G11:L11 A12:E12 G12:L12 A13:E13 G13:L13 A14:E14 G14:L14 A15:E15 G15:L15 A16:E16 G16:L16 A17:E17 G17:L17 A18:E18 G18:L18 A19:E19 G19:L19 A20:E20 G20:L20 A21:E21 G21:L21 A22:E22 G22:L22 A23:E23 G23:L23 A24:E24 G24:L24 A25:E25 G25:L25 A26:E26 G26:L26 A27:E27 G27:L27 A28:E28 G28:L28 A29:E29 G29:L29 A30:E30 G30:L30 A31:E31 G31:L31 A32:E32 G32:L32 A33:E33 G33:L33 A34:E34 G34:L34 A50:L50 A36:E36 G36:L36 A37:E37 G37:L37 A38:E38 G38:L38 A39:E39 G39:L39 A40:E40 G40:L40 A41:E41 G41:L41 A42:E42 G42:L42 A43:E43 G43:L43 A44:E44 G44:L44 A45:E45 G45:L45 A46:E46 G46:L46 A47:E47 G47:L47 A48:E48 G48:L48 A49:E49 G49:L49 A131:L131 A51:E51 G51:L51 A52:E52 G52:L52 A53:E53 G53:L53 A54:E54 G54:L54 A55:E55 G55:L55 A56:E56 G56:L56 A57:E57 G57:L57 A58:E58 G58:L58 A59:E59 G59:L59 A60:E60 G60:L60 A61:E61 G61:L61 A62:E62 G62:L62 A63:E63 G63:L63 A64:E64 G64:L64 A65:E65 G65:L65 A66:E66 G66:L66 A67:E67 G67:L67 A68:E68 G68:L68 A69:E69 G69:L69 A70:E70 G70:L70 A71:E71 G71:L71 A72:E72 G72:L72 A73:E73 G73:L73 A74:E74 G74:L74 A75:E75 G75:L75 A76:E76 G76:L76 A77:E77 G77:L77 A78:E78 G78:L78 A79:E79 G79:L79 A80:E80 G80:L80 A81:E81 G81:L81 A82:E82 G82:L82 A83:E83 G83:L83 A84:E84 G84:L84 A85:E85 G85:L85 A86:E86 G86:L86 A87:E87 G87:L87 A88:E88 G88:L88 A89:E89 G89:L89 A90:E90 G90:L90 A91:E91 G91:L91 A92:E92 G92:L92 A93:E93 G93:L93 A94:E94 G94:L94 A95:E95 G95:L95 A96:E96 G96:L96 A97:E97 G97:L97 A98:E98 G98:L98 A99:E99 G99:L99 A100:E100 G100:L100 A101:E101 G101:L101 A102:E102 G102:L102 A103:E103 G103:L103 A104:E104 G104:L104 A105:E105 G105:L105 A106:E106 G106:L106 A107:E107 G107:L107 A108:E108 G108:L108 A109:E109 G109:L109 A110:E110 G110:L110 A111:E111 G111:L111 A112:E112 G112:L112 A113:E113 G113:L113 A114:E114 G114:L114 A115:E115 G115:L115 A116:E116 G116:L116 A117:E117 G117:L117 A118:E118 G118:L118 A119:E119 G119:L119 A120:E120 G120:L120 A121:E121 G121:L121 A122:E122 G122:L122 A123:E123 G123:L123 A124:E124 G124:L124 A125:E125 G125:L125 A126:E126 G126:L126 A127:E127 G127:L127 A128:E128 G128:L128 A129:E129 G129:L129 A130:E130 G130:L130 A230:L230 A132:E132 G132:L132 A133:E133 G133:L133 A134:E134 G134:L134 A135:E135 G135:L135 A136:E136 G136:L136 A137:E137 G137:L137 A138:E138 G138:L138 A139:E139 G139:L139 A140:E140 G140:L140 A141:E141 G141:L141 A142:E142 G142:L142 A143:E143 G143:L143 A144:E144 G144:L144 A145:E145 G145:L145 A146:E146 G146:L146 A147:E147 G147:L147 A148:E148 G148:L148 A149:E149 G149:L149 A150:E150 G150:L150 A151:E151 G151:L151 A152:E152 G152:L152 A153:E153 G153:L153 A154:E154 G154:L154 A155:E155 G155:L155 A156:E156 G156:L156 A157:E157 G157:L157 A158:E158 G158:L158 A159:E159 G159:L159 A160:E160 G160:L160 A161:E161 G161:L161 A162:E162 G162:L162 A163:E163 G163:L163 A164:E164 G164:L164 A165:E165 G165:L165 A166:E166 G166:L166 A167:E167 G167:L167 A168:E168 G168:L168 A169:E169 G169:L169 A170:E170 G170:L170 A171:E171 G171:L171 A172:E172 G172:L172 A173:E173 G173:L173 A174:E174 G174:L174 A175:E175 G175:L175 A176:E176 G176:L176 A177:E177 G177:L177 A178:E178 G178:L178 A179:E179 G179:L179 A180:E180 G180:L180 A181:E181 G181:L181 A182:E182 G182:L182 A183:E183 G183:L183 A184:E184 G184:L184 A185:E185 G185:L185 A186:E186 G186:L186 A187:E187 G187:L187 A188:E188 G188:L188 A189:E189 G189:L189 A190:E190 G190:L190 A191:E191 G191:L191 A192:E192 G192:L192 A193:E193 G193:L193 A194:E194 G194:L194 A195:E195 G195:L195 A196:E196 G196:L196 A197:E197 G197:L197 A198:E198 G198:L198 A199:E199 G199:L199 A200:E200 G200:L200 A201:E201 G201:L201 A202:E202 G202:L202 A203:E203 G203:L203 A204:E204 G204:L204 A205:E205 G205:L205 A206:E206 G206:L206 A207:E207 G207:L207 A208:E208 G208:L208 A209:E209 G209:L209 A210:E210 G210:L210 A211:E211 G211:L211 A212:E212 G212:L212 A213:E213 G213:L213 A214:E214 G214:L214 A215:E215 G215:L215 A216:E216 G216:L216 A217:E217 G217:L217 A218:E218 G218:L218 A219:E219 G219:L219 A220:E220 G220:L220 A221:E221 G221:L221 A222:E222 G222:L222 A223:E223 G223:L223 A224:E224 G224:L224 A225:E225 G225:L225 A226:E226 G226:L226 A227:E227 G227:L227 A228:E228 G228:L228 A229:E229 G229:L229 A272:L272 A231:E231 G231:L231 A232:E232 G232:L232 A233:E233 G233:L233 A234:E234 G234:L234 A235:E235 G235:L235 A236:E236 G236:L236 A237:E237 G237:L237 A238:E238 G238:L238 A239:E239 G239:L239 A240:E240 G240:L240 A241:E241 G241:L241 A242:E242 G242:L242 A243:E243 G243:L243 A244:E244 G244:L244 A245:E245 G245:L245 A246:E246 G246:L246 A247:E247 G247:L247 A248:E248 G248:L248 A249:E249 G249:L249 A250:E250 G250:L250 A251:E251 G251:L251 A252:E252 G252:L252 A253:E253 G253:L253 A254:E254 G254:L254 A255:E255 G255:L255 A256:E256 G256:L256 A257:E257 G257:L257 A258:E258 G258:L258 A259:E259 G259:L259 A260:E260 G260:L260 A261:E261 G261:L261 A262:E262 G262:L262 A263:E263 G263:L263 A264:E264 G264:L264 A265:E265 G265:L265 A266:E266 G266:L266 A267:E267 G267:L267 A268:E268 G268:L268 A269:E269 G269:L269 A270:E270 G270:L270 A271:E271 G271:L271 A296:L296 A273:E273 G273:L273 A274:E274 G274:L274 A275:E275 G275:L275 A276:E276 G276:L276 A277:E277 G277:L277 A278:E278 G278:L278 A279:E279 G279:L279 A280:E280 G280:L280 A281:E281 G281:L281 A282:E282 G282:L282 A283:E283 G283:L283 A284:E284 G284:L284 A285:E285 G285:L285 A286:E286 G286:L286 A287:E287 G287:L287 A288:E288 G288:L288 A289:E289 G289:L289 A290:E290 G290:L290 A291:E291 G291:L291 A292:E292 G292:L292 A293:E293 G293:L293 A294:E294 G294:L294 A295:E295 G295:L295 A341:L352 A297:E297 G297:L297 A298:E298 G298:L298 A299:E299 G299:L299 A300:E300 G300:L300 A301:E301 G301:L301 A302:E302 G302:L302 A303:E303 G303:L303 A304:E304 G304:L304 A305:E305 G305:L305 A306:E306 G306:L306 A307:E307 G307:L307 A308:E308 G308:L308 A309:E309 G309:L309 A310:E310 G310:L310 A311:E311 G311:L311 A312:E312 G312:L312 A313:E313 G313:L313 A314:E314 G314:L314 A315:E315 G315:L315 A316:E316 G316:L316 A317:E317 G317:L317 A318:E318 G318:L318 A319:E319 G319:L319 A320:E320 G320:L320 A321:E321 G321:L321 A322:E322 G322:L322 A323:E323 G323:L323 A324:E324 G324:L324 A325:E325 G325:L325 A326:E326 G326:L326 A327:E327 G327:L327 A328:E328 G328:L328 A329:E329 G329:L329 A330:E330 G330:L330 A331:E331 G331:L331 A332:E332 G332:L332 A333:E333 G333:L333 A334:E334 G334:L334 A335:E335 G335:L335 A336:E336 G336:L336 A337:E337 G337:L337 A338:E338 G338:L338 A339:E339 G339:L339 A340:E340 G340:L340" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:L1 A230:L230 A168 C168:L168 A35:L35 A2:E2 G2:L2 A3:E3 G3:L3 A4:E4 G4:L4 A5:E5 G5:L5 A6:E6 G6:L6 A7:E7 G7:L7 A8:E8 G8:L8 A9:E9 G9:L9 A10:E10 G10:L10 A11:E11 G11:L11 A12:E12 G12:L12 A13:E13 G13:L13 A14:E14 G14:L14 A15:E15 G15:L15 A16:E16 G16:L16 A17:E17 G17:L17 A18:E18 G18:L18 A19:E19 G19:L19 A20:E20 G20:L20 A21:E21 G21:L21 A22:E22 G22:L22 A23:E23 G23:L23 A24:E24 G24:L24 A25:E25 G25:L25 A26:E26 G26:L26 A27:E27 G27:L27 A28:E28 G28:L28 A29:E29 G29:L29 A30:E30 G30:L30 A31:E31 G31:L31 A32:E32 G32:L32 A33:E33 G33:L33 A34:E34 G34:L34 A50:L50 A36:E36 G36:L36 A37:E37 G37:L37 A38:E38 G38:L38 A39:E39 G39:L39 A40:E40 G40:L40 A41:E41 G41:L41 A42:E42 G42:L42 A43:E43 G43:L43 A44:E44 G44:L44 A45:E45 G45:L45 A46:E46 G46:L46 A47:E47 G47:L47 A48:E48 G48:L48 A49:E49 G49:L49 A131:L131 A51:E51 G51:L51 A52:E52 G52:L52 A53:E53 G53:L53 A54:E54 G54:L54 A55:E55 G55:L55 A56:E56 G56:L56 A57:E57 G57:L57 A58:E58 G58:L58 A59:E59 G59:L59 A60:E60 G60:L60 A61:E61 G61:L61 A62:E62 G62:L62 A63:E63 G63:L63 A64:E64 G64:L64 A65:E65 G65:L65 A66:E66 G66:L66 A67:E67 G67:L67 A68:E68 G68:L68 A69:E69 G69:L69 A70:E70 G70:L70 A71:E71 G71:L71 A72:E72 G72:L72 A73:E73 G73:L73 A74:E74 G74:L74 A75:E75 G75:L75 A76:E76 G76:L76 A77:E77 G77:L77 A78:E78 G78:L78 A79:E79 G79:L79 A80:E80 G80:L80 A81:E81 G81:L81 A82:E82 G82:L82 A83:E83 G83:L83 A84:E84 G84:L84 A85:E85 G85:L85 A86:E86 G86:L86 A87:E87 G87:L87 A88:E88 G88:L88 A89:E89 G89:L89 A90:E90 G90:L90 A91:E91 G91:L91 A92:E92 G92:L92 A93:E93 G93:L93 A94:E94 G94:L94 A95:E95 G95:L95 A96:E96 G96:L96 A97:E97 G97:L97 A98:E98 G98:L98 A99:E99 G99:L99 A100:E100 G100:L100 A101:E101 G101:L101 A102:E102 G102:L102 A103:E103 G103:L103 A104:E104 G104:L104 A105:E105 G105:L105 A106:E106 G106:L106 A107:E107 G107:L107 A108:E108 G108:L108 A109:E109 G109:L109 A110:E110 G110:L110 A111:E111 G111:L111 A112:E112 G112:L112 A113:E113 G113:L113 A114:E114 G114:L114 A115:E115 G115:L115 A116:E116 G116:L116 A117:E117 G117:L117 A118:E118 G118:L118 A119:E119 G119:L119 A120:E120 G120:L120 A121:E121 G121:L121 A122:E122 G122:L122 A123:E123 G123:L123 A124:E124 G124:L124 A125:E125 G125:L125 A126:E126 G126:L126 A127:E127 G127:L127 A128:E128 G128:L128 A129:E129 G129:L129 A130:E130 G130:L130 A167:E167 A132:E132 G132:L132 A133:E133 G133:L133 A134:E134 G134:L134 A135:E135 G135:L135 A136:E136 G136:L136 A137:E137 G137:L137 A138:E138 G138:L138 A139:E139 G139:L139 A140:E140 G140:L140 A141:E141 G141:L141 A142:E142 G142:L142 A143:E143 G143:L143 A144:E144 G144:L144 A145:E145 G145:L145 A146:E146 G146:L146 A147:E147 G147:L147 A148:E148 G148:L148 A149:E149 G149:L149 A150:E150 G150:L150 A151:E151 G151:L151 A152:E152 G152:L152 A153:E153 G153:L153 A154:E154 G154:L154 A155:E155 G155:L155 A156:E156 G156:L156 A157:E157 G157:L157 A158:E158 G158:L158 A159:E159 G159:L159 A160:E160 G160:L160 A161:E161 G161:L161 A162:E162 G162:L162 A163:E163 G163:L163 A164:E164 G164:L164 A165:E165 G165:L165 A166:E166 G166:L166 G167:L167 A169:E169 G169:L169 A170:E170 G170:L170 A171:E171 G171:L171 A172:E172 G172:L172 A173:E173 G173:L173 A174:E174 G174:L174 A175:E175 G175:L175 A176:E176 G176:L176 A177:E177 G177:L177 A178:E178 G178:L178 A179:E179 G179:L179 A180:E180 G180:L180 A181:E181 G181:L181 A182:E182 G182:L182 A183:E183 G183:L183 A184:E184 G184:L184 A185:E185 G185:L185 A186:E186 G186:L186 A187:E187 G187:L187 A188:E188 G188:L188 A189:E189 G189:L189 A190:E190 G190:L190 A191:E191 G191:L191 A192:E192 G192:L192 A193:E193 G193:L193 A194:E194 G194:L194 A195:E195 G195:L195 A196:E196 G196:L196 A197:E197 G197:L197 A198:E198 G198:L198 A199:E199 G199:L199 A200:E200 G200:L200 A201:E201 G201:L201 A202:E202 G202:L202 A203:E203 G203:L203 A204:E204 G204:L204 A205:E205 G205:L205 A206:E206 G206:L206 A207:E207 G207:L207 A208:E208 G208:L208 A209:E209 G209:L209 A210:E210 G210:L210 A211:E211 G211:L211 A212:E212 G212:L212 A213:E213 G213:L213 A214:E214 G214:L214 A215:E215 G215:L215 A216:E216 G216:L216 A217:E217 G217:L217 A218:E218 G218:L218 A219:E219 G219:L219 A220:E220 G220:L220 A221:E221 G221:L221 A222:E222 G222:L222 A223:E223 G223:L223 A224:E224 G224:L224 A225:E225 G225:L225 A226:E226 G226:L226 A227:E227 G227:L227 A228:E228 G228:L228 A229:E229 G229:L229 A272:L272 A231:E231 G231:L231 A232:E232 G232:L232 A233:E233 G233:L233 A234:E234 G234:L234 A235:E235 G235:L235 A236:E236 G236:L236 A237:E237 G237:L237 A238:E238 G238:L238 A239:E239 G239:L239 A240:E240 G240:L240 A241:E241 G241:L241 A242:E242 G242:L242 A243:E243 G243:L243 A244:E244 G244:L244 A245:E245 G245:L245 A246:E246 G246:L246 A247:E247 G247:L247 A248:E248 G248:L248 A249:E249 G249:L249 A250:E250 G250:L250 A251:E251 G251:L251 A252:E252 G252:L252 A253:E253 G253:L253 A254:E254 G254:L254 A255:E255 G255:L255 A256:E256 G256:L256 A257:E257 G257:L257 A258:E258 G258:L258 A259:E259 G259:L259 A260:E260 G260:L260 A261:E261 G261:L261 A262:E262 G262:L262 A263:E263 G263:L263 A264:E264 G264:L264 A265:E265 G265:L265 A266:E266 G266:L266 A267:E267 G267:L267 A268:E268 G268:L268 A269:E269 G269:L269 A270:E270 G270:L270 A271:E271 G271:L271 A296:L296 A273:E273 G273:L273 A274:E274 G274:L274 A275:E275 G275:L275 A276:E276 G276:L276 A277:E277 G277:L277 A278:E278 G278:L278 A279:E279 G279:L279 A280:E280 G280:L280 A281:E281 G281:L281 A282:E282 G282:L282 A283:E283 G283:L283 A284:E284 G284:L284 A285:E285 G285:L285 A286:E286 G286:L286 A287:E287 G287:L287 A288:E288 G288:L288 A289:E289 G289:L289 A290:E290 G290:L290 A291:E291 G291:L291 A292:E292 G292:L292 A293:E293 G293:L293 A294:E294 G294:L294 A295:E295 G295:L295 A341:L352 A297:E297 G297:L297 A298:E298 G298:L298 A299:E299 G299:L299 A300:E300 G300:L300 A301:E301 G301:L301 A302:E302 G302:L302 A303:E303 G303:L303 A304:E304 G304:L304 A305:E305 G305:L305 A306:E306 G306:L306 A307:E307 G307:L307 A308:E308 G308:L308 A309:E309 G309:L309 A310:E310 G310:L310 A311:E311 G311:L311 A312:E312 G312:L312 A313:E313 G313:L313 A314:E314 G314:L314 A315:E315 G315:L315 A316:E316 G316:L316 A317:E317 G317:L317 A318:E318 G318:L318 A319:E319 G319:L319 A320:E320 G320:L320 A321:E321 G321:L321 A322:E322 G322:L322 A323:E323 G323:L323 A324:E324 G324:L324 A325:E325 G325:L325 A326:E326 G326:L326 A327:E327 G327:L327 A328:E328 G328:L328 A329:E329 G329:L329 A330:E330 G330:L330 A331:E331 G331:L331 A332:E332 G332:L332 A333:E333 G333:L333 A334:E334 G334:L334 A335:E335 G335:L335 A336:E336 G336:L336 A337:E337 G337:L337 A338:E338 G338:L338 A339:E339 G339:L339 A340:E340 G340:L340" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>